--- a/docs/oc-mensuales/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/sep-2026.xlsx
+++ b/docs/oc-mensuales/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/sep-2026.xlsx
@@ -684,7 +684,11 @@
           <t>15.751.336-2</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +749,11 @@
           <t>76.791.832-1</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +875,11 @@
           <t>76.791.832-1</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +940,11 @@
           <t>76.791.832-1</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1188,11 @@
           <t>15.751.336-2</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1314,11 @@
           <t>76.791.832-1</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2392,7 +2416,11 @@
           <t>77.850.715-3</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2575,7 +2603,11 @@
           <t>77.498.695-2</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2941,7 +2973,11 @@
           <t>77.852.175-K</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3185,7 +3221,11 @@
           <t>77.852.175-K</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3246,7 +3286,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4039,7 +4083,11 @@
           <t>76.791.832-1</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4649,7 +4697,11 @@
           <t>76.791.832-1</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-mensuales/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/sep-2026.xlsx
+++ b/docs/oc-mensuales/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/sep-2026.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M74"/>
+  <dimension ref="A1:M75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4161,7 +4161,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1077367-61-CM26</t>
+          <t>2735-1197-CM26</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4186,27 +4186,27 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>61.607.301-k</t>
+          <t>69.255.200-8</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
+          <t>I MUNICIPALIDAD LO BARNECHEA</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>TURISMO AYEKANTUN LIMITADA</t>
+          <t>AUTOMOTRIZ R Y R LIMITADA</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>76.470.279-4</t>
+          <t>77.951.690-3</t>
         </is>
       </c>
       <c r="K61" t="inlineStr"/>
@@ -4216,13 +4216,13 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>41230.37</v>
+        <v>27536.25</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>3517-190-CM26</t>
+          <t>1057417-16197-CM26</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4247,27 +4247,27 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>69.180.700-2</t>
+          <t>61.607.301-K</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE TRAIGUEN</t>
+          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>TRANSPORTES KADIMA LIMITADA</t>
+          <t>TURISMO AYEKANTUN LIMITADA</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>76.336.696-0</t>
+          <t>76.470.279-4</t>
         </is>
       </c>
       <c r="K62" t="inlineStr"/>
@@ -4277,13 +4277,13 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>18282.18</v>
+        <v>22013.99</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2735-1197-CM26</t>
+          <t>1077367-61-CM26</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4308,27 +4308,27 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>69.255.200-8</t>
+          <t>61.607.301-k</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD LO BARNECHEA</t>
+          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ R Y R LIMITADA</t>
+          <t>TURISMO AYEKANTUN LIMITADA</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>77.951.690-3</t>
+          <t>76.470.279-4</t>
         </is>
       </c>
       <c r="K63" t="inlineStr"/>
@@ -4338,13 +4338,13 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>27536.25</v>
+        <v>41230.37</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>1057417-16197-CM26</t>
+          <t>3517-190-CM26</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4369,27 +4369,27 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>61.607.301-K</t>
+          <t>69.180.700-2</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
+          <t>MUNICIPALIDAD DE TRAIGUEN</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>TURISMO AYEKANTUN LIMITADA</t>
+          <t>TRANSPORTES KADIMA LIMITADA</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>76.470.279-4</t>
+          <t>76.336.696-0</t>
         </is>
       </c>
       <c r="K64" t="inlineStr"/>
@@ -4399,13 +4399,13 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>22013.99</v>
+        <v>18282.18</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>3192-95-CM26</t>
+          <t>1469-2817-CM26</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4430,27 +4430,27 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>61.102.090-2</t>
+          <t>70.885.500-6</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>UNIVERSIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Felipe </t>
+          <t>BUSES VILLAR</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>76.834.013-7</t>
+          <t>76.465.610-5</t>
         </is>
       </c>
       <c r="K65" t="inlineStr"/>
@@ -4460,13 +4460,13 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>4028.12</v>
+        <v>35010.51</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2467-1224-CM26</t>
+          <t>3192-95-CM26</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4491,27 +4491,27 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>69.140.900-7</t>
+          <t>61.102.090-2</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHILLAN</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Julio Saavedra</t>
+          <t xml:space="preserve">Felipe </t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>76.248.427-7</t>
+          <t>76.834.013-7</t>
         </is>
       </c>
       <c r="K66" t="inlineStr"/>
@@ -4521,13 +4521,13 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>1625.75</v>
+        <v>4028.12</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>1469-2817-CM26</t>
+          <t>2467-1224-CM26</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4552,27 +4552,27 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>70.885.500-6</t>
+          <t>69.140.900-7</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TALCA</t>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>BUSES VILLAR</t>
+          <t>Julio Saavedra</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>76.465.610-5</t>
+          <t>76.248.427-7</t>
         </is>
       </c>
       <c r="K67" t="inlineStr"/>
@@ -4582,7 +4582,7 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>35010.51</v>
+        <v>1625.75</v>
       </c>
     </row>
     <row r="68">
@@ -4714,7 +4714,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2427-889-CM26</t>
+          <t>1300-317-SE26</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4739,37 +4739,41 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>69.060.900-2</t>
+          <t>61.961.000-8</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VALPARAISO</t>
+          <t>SERVICIO NACIONAL DEL ADULTO MAYOR</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Empresa de Transportes Pablo Jaramillo Benavente E</t>
+          <t>YANGUAS TRANSPORTE TURISTICO</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>76.076.244-k</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr"/>
+          <t>78.973.230-2</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>32577.09</v>
+        <v>866.25</v>
       </c>
     </row>
     <row r="71">
@@ -4958,7 +4962,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>1059109-101-CM26</t>
+          <t>2427-889-CM26</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4973,7 +4977,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -4983,27 +4987,27 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>69.060.900-2</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>I MUNICIPALIDAD DE VALPARAISO</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Felipe </t>
+          <t>Empresa de Transportes Pablo Jaramillo Benavente E</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>76.834.013-7</t>
+          <t>76.076.244-k</t>
         </is>
       </c>
       <c r="K74" t="inlineStr"/>
@@ -5013,6 +5017,67 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
+        <v>32577.09</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1059109-101-CM26</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>61.107.000-4</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Felipe </t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>76.834.013-7</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="n">
         <v>926.26</v>
       </c>
     </row>

--- a/docs/oc-mensuales/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/sep-2026.xlsx
+++ b/docs/oc-mensuales/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/sep-2026.xlsx
@@ -534,7 +534,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -721,7 +721,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -751,7 +751,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -942,7 +942,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1038,7 +1038,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1316,7 +1316,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1534,7 +1534,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2144,7 +2144,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -3132,7 +3132,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -3193,7 +3193,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -3323,7 +3323,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -3384,7 +3384,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -3445,7 +3445,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -3628,7 +3628,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -3656,7 +3656,11 @@
           <t>76.701.245-4</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3689,7 +3693,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -3717,7 +3721,11 @@
           <t>76.701.245-4</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3933,7 +3941,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -4085,7 +4093,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -4699,7 +4707,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -4734,7 +4742,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -4799,7 +4807,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -5043,7 +5051,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">

--- a/docs/oc-mensuales/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/sep-2026.xlsx
+++ b/docs/oc-mensuales/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/sep-2026.xlsx
@@ -4929,7 +4929,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
